--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/OREGON_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/OREGON_2017.xlsx
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C213">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C711">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C758">
